--- a/output/Data and Chart Outputs/netherlands_power_capacity_annual.xlsx
+++ b/output/Data and Chart Outputs/netherlands_power_capacity_annual.xlsx
@@ -1796,7 +1796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1830,6 +1830,16 @@
           <t>Difference (%)</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ours, end of same year (MW)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Difference same year (%)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
@@ -1852,6 +1862,12 @@
       <c r="F2" t="n">
         <v>-2.6</v>
       </c>
+      <c r="G2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
@@ -1874,6 +1890,12 @@
       <c r="F3" t="n">
         <v>-5.8</v>
       </c>
+      <c r="G3" t="n">
+        <v>17402</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-5.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
@@ -1896,6 +1918,12 @@
       <c r="F4" t="n">
         <v>-13.4</v>
       </c>
+      <c r="G4" t="n">
+        <v>7646</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -1918,6 +1946,12 @@
       <c r="F5" t="n">
         <v>-25</v>
       </c>
+      <c r="G5" t="n">
+        <v>14823</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
@@ -1940,6 +1974,12 @@
       <c r="F6" t="n">
         <v>-14.5</v>
       </c>
+      <c r="G6" t="n">
+        <v>3431</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-14.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -1962,6 +2002,12 @@
       <c r="F7" t="n">
         <v>5.6</v>
       </c>
+      <c r="G7" t="n">
+        <v>512</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -2010,6 +2056,12 @@
       <c r="F10" t="n">
         <v>-47.9</v>
       </c>
+      <c r="G10" t="n">
+        <v>407</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-47.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -2032,6 +2084,12 @@
       <c r="F11" t="n">
         <v>-15.6</v>
       </c>
+      <c r="G11" t="n">
+        <v>44259</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-5.6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
@@ -2080,6 +2138,12 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
+      <c r="G14" t="n">
+        <v>38</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -2102,6 +2166,12 @@
       <c r="F15" t="n">
         <v>-6.1</v>
       </c>
+      <c r="G15" t="n">
+        <v>17460</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-5.8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
@@ -2124,6 +2194,12 @@
       <c r="F16" t="n">
         <v>-1.6</v>
       </c>
+      <c r="G16" t="n">
+        <v>8700</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -2146,6 +2222,12 @@
       <c r="F17" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G17" t="n">
+        <v>17356</v>
+      </c>
+      <c r="H17" t="n">
+        <v>16.4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
@@ -2168,6 +2250,12 @@
       <c r="F18" t="n">
         <v>-14.4</v>
       </c>
+      <c r="G18" t="n">
+        <v>3431</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-14.4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -2190,6 +2278,12 @@
       <c r="F19" t="n">
         <v>5.3</v>
       </c>
+      <c r="G19" t="n">
+        <v>512</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -2238,6 +2332,12 @@
       <c r="F22" t="n">
         <v>-46.7</v>
       </c>
+      <c r="G22" t="n">
+        <v>407</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-46.7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -2260,6 +2360,12 @@
       <c r="F23" t="n">
         <v>-6</v>
       </c>
+      <c r="G23" t="n">
+        <v>47904</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.8</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
@@ -2308,6 +2414,12 @@
       <c r="F26" t="n">
         <v>0</v>
       </c>
+      <c r="G26" t="n">
+        <v>38</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -2330,6 +2442,12 @@
       <c r="F27" t="n">
         <v>-6.4</v>
       </c>
+      <c r="G27" t="n">
+        <v>17500</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-6.2</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -2352,6 +2470,12 @@
       <c r="F28" t="n">
         <v>-24.3</v>
       </c>
+      <c r="G28" t="n">
+        <v>10802</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -2374,6 +2498,12 @@
       <c r="F29" t="n">
         <v>-28.6</v>
       </c>
+      <c r="G29" t="n">
+        <v>21957</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-9.6</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -2396,6 +2526,12 @@
       <c r="F30" t="n">
         <v>-14.5</v>
       </c>
+      <c r="G30" t="n">
+        <v>3431</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-14.5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -2418,6 +2554,12 @@
       <c r="F31" t="n">
         <v>5.3</v>
       </c>
+      <c r="G31" t="n">
+        <v>512</v>
+      </c>
+      <c r="H31" t="n">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
@@ -2466,6 +2608,12 @@
       <c r="F34" t="n">
         <v>-39.3</v>
       </c>
+      <c r="G34" t="n">
+        <v>407</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-39.3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -2488,6 +2636,12 @@
       <c r="F35" t="n">
         <v>-20.3</v>
       </c>
+      <c r="G35" t="n">
+        <v>54647</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -2520,6 +2674,9 @@
       <c r="E37" t="n">
         <v>132</v>
       </c>
+      <c r="G37" t="n">
+        <v>229</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -2542,6 +2699,12 @@
       <c r="F38" t="n">
         <v>0</v>
       </c>
+      <c r="G38" t="n">
+        <v>38</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -2564,6 +2727,12 @@
       <c r="F39" t="n">
         <v>-5.3</v>
       </c>
+      <c r="G39" t="n">
+        <v>17537</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-5.1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -2586,6 +2755,12 @@
       <c r="F40" t="n">
         <v>-7.6</v>
       </c>
+      <c r="G40" t="n">
+        <v>11702</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -2608,6 +2783,12 @@
       <c r="F41" t="n">
         <v>-21.5</v>
       </c>
+      <c r="G41" t="n">
+        <v>24772</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-11.5</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -2630,6 +2811,12 @@
       <c r="F42" t="n">
         <v>-14.5</v>
       </c>
+      <c r="G42" t="n">
+        <v>3431</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-14.5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -2652,6 +2839,12 @@
       <c r="F43" t="n">
         <v>5.3</v>
       </c>
+      <c r="G43" t="n">
+        <v>512</v>
+      </c>
+      <c r="H43" t="n">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -2700,6 +2893,12 @@
       <c r="F46" t="n">
         <v>-47.7</v>
       </c>
+      <c r="G46" t="n">
+        <v>407</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-47.7</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -2722,6 +2921,12 @@
       <c r="F47" t="n">
         <v>-14.5</v>
       </c>
+      <c r="G47" t="n">
+        <v>58399</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-8.6</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
@@ -2754,6 +2959,9 @@
       <c r="E49" t="n">
         <v>229</v>
       </c>
+      <c r="G49" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -2776,6 +2984,12 @@
       <c r="F50" t="n">
         <v>0</v>
       </c>
+      <c r="G50" t="n">
+        <v>38</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -2798,6 +3012,12 @@
       <c r="F51" t="n">
         <v>-4.8</v>
       </c>
+      <c r="G51" t="n">
+        <v>17394</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-5.5</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -2820,6 +3040,12 @@
       <c r="F52" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G52" t="n">
+        <v>11782</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-1.1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -2842,6 +3068,12 @@
       <c r="F53" t="n">
         <v>-15.4</v>
       </c>
+      <c r="G53" t="n">
+        <v>25901</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-11.5</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -2864,6 +3096,12 @@
       <c r="F54" t="n">
         <v>-14.5</v>
       </c>
+      <c r="G54" t="n">
+        <v>3431</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-14.5</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -2886,6 +3124,12 @@
       <c r="F55" t="n">
         <v>5.3</v>
       </c>
+      <c r="G55" t="n">
+        <v>512</v>
+      </c>
+      <c r="H55" t="n">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -2934,6 +3178,12 @@
       <c r="F58" t="n">
         <v>-47.7</v>
       </c>
+      <c r="G58" t="n">
+        <v>407</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-47.7</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -2956,6 +3206,12 @@
       <c r="F59" t="n">
         <v>-10.6</v>
       </c>
+      <c r="G59" t="n">
+        <v>59465</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
@@ -2986,6 +3242,9 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
+        <v>350</v>
+      </c>
+      <c r="G61" t="n">
         <v>350</v>
       </c>
     </row>
